--- a/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0-ballot</t>
+    <t>2.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-25T10:44:45+00:00</t>
+    <t>2024-03-25T10:59:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-25T10:59:40+00:00</t>
+    <t>2024-03-25T11:06:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-23T08:02:06+00:00</t>
+    <t>2024-05-23T12:05:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-23T12:05:52+00:00</t>
+    <t>2024-05-23T12:32:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-23T12:32:02+00:00</t>
+    <t>2024-05-23T14:35:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-23T14:35:00+00:00</t>
+    <t>2024-06-11T15:33:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -12743,7 +12743,7 @@
         <v>83</v>
       </c>
       <c r="X83" t="s" s="2">
-        <v>248</v>
+        <v>158</v>
       </c>
       <c r="Y83" t="s" s="2">
         <v>606</v>
@@ -15287,7 +15287,7 @@
         <v>83</v>
       </c>
       <c r="X104" t="s" s="2">
-        <v>248</v>
+        <v>158</v>
       </c>
       <c r="Y104" t="s" s="2">
         <v>606</v>
@@ -15409,7 +15409,7 @@
         <v>83</v>
       </c>
       <c r="X105" t="s" s="2">
-        <v>248</v>
+        <v>158</v>
       </c>
       <c r="Y105" t="s" s="2">
         <v>606</v>
@@ -18803,7 +18803,7 @@
         <v>83</v>
       </c>
       <c r="X133" t="s" s="2">
-        <v>248</v>
+        <v>158</v>
       </c>
       <c r="Y133" t="s" s="2">
         <v>606</v>
@@ -18925,7 +18925,7 @@
         <v>83</v>
       </c>
       <c r="X134" t="s" s="2">
-        <v>248</v>
+        <v>158</v>
       </c>
       <c r="Y134" t="s" s="2">
         <v>606</v>
@@ -22319,7 +22319,7 @@
         <v>83</v>
       </c>
       <c r="X162" t="s" s="2">
-        <v>248</v>
+        <v>158</v>
       </c>
       <c r="Y162" t="s" s="2">
         <v>606</v>

--- a/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T15:33:12+00:00</t>
+    <t>2024-06-11T15:33:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T15:33:34+00:00</t>
+    <t>2024-07-02T12:51:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -75,7 +75,7 @@
     <t>Interop'Santé (http://interopsante.org/)</t>
   </si>
   <si>
-    <t>InteropSanté (fhir@interopsante.org(WORK))</t>
+    <t>InteropSanté (fhir@interopsante.org(work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-08T11:39:28+00:00</t>
+    <t>2024-07-17T12:13:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T12:13:27+00:00</t>
+    <t>2024-07-17T14:21:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.1</t>
+    <t>2.1.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T14:21:13+00:00</t>
+    <t>2024-07-17T15:15:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T15:15:49+00:00</t>
+    <t>2024-07-17T15:35:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-25T07:11:02+00:00</t>
+    <t>2024-07-25T15:28:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-25T15:28:42+00:00</t>
+    <t>2024-07-25T15:29:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-25T15:29:18+00:00</t>
+    <t>2024-07-25T15:44:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-25T15:44:10+00:00</t>
+    <t>2024-08-01T13:12:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.1.0-ballot</t>
+    <t>2.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-03T15:38:30+00:00</t>
+    <t>2024-09-04T07:28:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-04T07:28:39+00:00</t>
+    <t>2024-09-04T07:33:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-06T12:53:53+00:00</t>
+    <t>2024-10-28T08:07:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -446,7 +446,7 @@
     <t>Identifies where the resource comes from</t>
   </si>
   <si>
-    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
+    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
   </si>
   <si>
     <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
@@ -466,7 +466,7 @@
     <t>Profiles this resource claims to conform to</t>
   </si>
   <si>
-    <t>A list of profiles (references to [StructureDefinition](structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](structuredefinition-definitions.html#StructureDefinition.url).</t>
+    <t>A list of profiles (references to [StructureDefinition](http://hl7.org/fhir/R4/structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](http://hl7.org/fhir/R4/structuredefinition-definitions.html#StructureDefinition.url).</t>
   </si>
   <si>
     <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>

--- a/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-28T08:07:18+00:00</t>
+    <t>2024-10-28T08:08:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-28T08:08:30+00:00</t>
+    <t>2024-10-29T10:42:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-28T09:05:50+00:00</t>
+    <t>2025-01-28T09:07:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-28T09:07:36+00:00</t>
+    <t>2025-02-04T08:51:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-04T08:51:44+00:00</t>
+    <t>2025-02-04T09:30:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-04T09:30:35+00:00</t>
+    <t>2025-02-19T13:47:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T13:47:59+00:00</t>
+    <t>2025-02-19T13:52:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T13:52:01+00:00</t>
+    <t>2025-02-19T13:53:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T13:53:58+00:00</t>
+    <t>2025-02-19T13:58:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T13:58:46+00:00</t>
+    <t>2025-02-19T14:07:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T14:07:54+00:00</t>
+    <t>2025-02-19T14:26:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-12T08:11:18+00:00</t>
+    <t>2025-05-20T13:27:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T13:27:17+00:00</t>
+    <t>2025-05-20T13:29:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T13:29:42+00:00</t>
+    <t>2025-05-20T13:48:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6287" uniqueCount="754">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6288" uniqueCount="755">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T13:48:39+00:00</t>
+    <t>2025-06-04T13:32:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -653,7 +653,7 @@
     <t>supportingInfo</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {workflow-supportingInfo}
+    <t xml:space="preserve">Extension {workflow-supportingInfo|5.2.0}
 </t>
   </si>
   <si>
@@ -1492,7 +1492,7 @@
 If the use case requires BodySite to be handled as a separate resource (e.g. to identify and track separately) then use the standard extension[ bodySite](http://hl7.org/fhir/extension-bodysite.html).</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/hspc/ValueSet/bpMeasBodyLocationPrecoordVS</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-spo2-body-location</t>
   </si>
   <si>
     <t>&lt; 123037004 |Body structure|</t>
@@ -1522,7 +1522,7 @@
     <t>In some cases, method can impact results and is thus used for determining whether results can be compared or determining significance of results.</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-bp-measurement-method</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-bp-meas-method</t>
   </si>
   <si>
     <t>OBX-17</t>
@@ -2312,6 +2312,9 @@
   </si>
   <si>
     <t>Observation.component:MeanBP.code.coding</t>
+  </si>
+  <si>
+    <t>Erroneous slicing wainting for R5 correction</t>
   </si>
   <si>
     <t>Observation.component:MeanBP.code.coding:MBPCode</t>
@@ -2709,7 +2712,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="84.54296875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="56.12109375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="50.95703125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.4453125" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
@@ -20778,7 +20781,9 @@
       <c r="AB150" t="s" s="2">
         <v>352</v>
       </c>
-      <c r="AC150" s="2"/>
+      <c r="AC150" t="s" s="2">
+        <v>739</v>
+      </c>
       <c r="AD150" t="s" s="2">
         <v>83</v>
       </c>
@@ -20821,13 +20826,13 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="B151" t="s" s="2">
         <v>619</v>
       </c>
       <c r="C151" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="D151" t="s" s="2">
         <v>83</v>
@@ -20945,7 +20950,7 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="B152" t="s" s="2">
         <v>625</v>
@@ -21063,7 +21068,7 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="B153" t="s" s="2">
         <v>627</v>
@@ -21183,7 +21188,7 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="B154" t="s" s="2">
         <v>629</v>
@@ -21228,10 +21233,10 @@
       </c>
       <c r="Q154" s="2"/>
       <c r="R154" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S154" t="s" s="2">
         <v>361</v>
-      </c>
-      <c r="S154" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="T154" t="s" s="2">
         <v>83</v>
@@ -21305,7 +21310,7 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="B155" t="s" s="2">
         <v>631</v>
@@ -21425,7 +21430,7 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="B156" t="s" s="2">
         <v>633</v>
@@ -21468,10 +21473,10 @@
       </c>
       <c r="Q156" s="2"/>
       <c r="R156" t="s" s="2">
-        <v>746</v>
+        <v>83</v>
       </c>
       <c r="S156" t="s" s="2">
-        <v>83</v>
+        <v>747</v>
       </c>
       <c r="T156" t="s" s="2">
         <v>83</v>
@@ -21545,7 +21550,7 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="B157" t="s" s="2">
         <v>636</v>
@@ -21665,7 +21670,7 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="B158" t="s" s="2">
         <v>638</v>
@@ -21787,7 +21792,7 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="B159" t="s" s="2">
         <v>640</v>
@@ -21909,7 +21914,7 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="B160" t="s" s="2">
         <v>589</v>
@@ -22031,7 +22036,7 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="B161" t="s" s="2">
         <v>598</v>
@@ -22153,7 +22158,7 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="B162" t="s" s="2">
         <v>603</v>
@@ -22275,7 +22280,7 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="B163" t="s" s="2">
         <v>604</v>

--- a/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-04T13:32:30+00:00</t>
+    <t>2025-06-24T17:01:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-24T17:01:22+00:00</t>
+    <t>2025-07-04T12:19:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-04T12:19:33+00:00</t>
+    <t>2025-07-08T13:28:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-08T13:28:39+00:00</t>
+    <t>2025-07-16T09:34:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-16T09:34:35+00:00</t>
+    <t>2025-07-30T14:55:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6288" uniqueCount="755">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6288" uniqueCount="756">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-30T14:55:53+00:00</t>
+    <t>2025-10-08T07:32:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -653,7 +653,7 @@
     <t>supportingInfo</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {workflow-supportingInfo|5.2.0}
+    <t xml:space="preserve">Extension {workflow-supportingInfo|5.3.0-ballot-tc1}
 </t>
   </si>
   <si>
@@ -661,6 +661,10 @@
   </si>
   <si>
     <t>Other resources *from the patient record* that may be relevant to the event.  The information from these resources was either used to create the instance or is provided to help with its interpretation.  This extension **should not** be used if more specific  inline elements  or extensions are available.  For example, use `Observation.hasMember`  instead of supportingInformation for  representing the members of an Observation panel.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1
+</t>
   </si>
   <si>
     <t>Observation.modifierExtension</t>
@@ -4988,7 +4992,7 @@
         <v>82</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>83</v>
+        <v>207</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>123</v>
@@ -5014,10 +5018,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -5043,16 +5047,16 @@
         <v>115</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="N20" t="s" s="2">
         <v>118</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>83</v>
@@ -5101,7 +5105,7 @@
         <v>83</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>81</v>
@@ -5136,10 +5140,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -5162,17 +5166,17 @@
         <v>95</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>83</v>
@@ -5221,7 +5225,7 @@
         <v>83</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>81</v>
@@ -5236,19 +5240,19 @@
         <v>106</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>83</v>
@@ -5256,14 +5260,14 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -5282,17 +5286,17 @@
         <v>95</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>83</v>
@@ -5341,7 +5345,7 @@
         <v>83</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>81</v>
@@ -5356,16 +5360,16 @@
         <v>106</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>83</v>
@@ -5376,14 +5380,14 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -5402,16 +5406,16 @@
         <v>95</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -5461,7 +5465,7 @@
         <v>83</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>81</v>
@@ -5476,16 +5480,16 @@
         <v>106</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>83</v>
@@ -5496,10 +5500,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5525,16 +5529,16 @@
         <v>174</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>83</v>
@@ -5559,11 +5563,11 @@
         <v>83</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Y24" s="2"/>
       <c r="Z24" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>83</v>
@@ -5581,7 +5585,7 @@
         <v>83</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>94</v>
@@ -5596,19 +5600,19 @@
         <v>106</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>83</v>
@@ -5616,10 +5620,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5642,19 +5646,19 @@
         <v>83</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>83</v>
@@ -5682,16 +5686,16 @@
         <v>178</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AC25" s="2"/>
       <c r="AD25" t="s" s="2">
@@ -5701,7 +5705,7 @@
         <v>121</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>81</v>
@@ -5725,10 +5729,10 @@
         <v>83</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>83</v>
@@ -5736,13 +5740,13 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C26" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D26" t="s" s="2">
         <v>83</v>
@@ -5764,19 +5768,19 @@
         <v>83</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>83</v>
@@ -5804,10 +5808,10 @@
         <v>178</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>83</v>
@@ -5825,7 +5829,7 @@
         <v>83</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>81</v>
@@ -5849,10 +5853,10 @@
         <v>83</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>83</v>
@@ -5860,10 +5864,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5978,10 +5982,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -6098,10 +6102,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -6127,16 +6131,16 @@
         <v>152</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>83</v>
@@ -6185,7 +6189,7 @@
         <v>83</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>81</v>
@@ -6206,10 +6210,10 @@
         <v>83</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>83</v>
@@ -6220,10 +6224,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6338,10 +6342,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6458,10 +6462,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6487,23 +6491,23 @@
         <v>136</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q32" s="2"/>
       <c r="R32" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="S32" t="s" s="2">
         <v>83</v>
@@ -6545,7 +6549,7 @@
         <v>83</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
@@ -6566,10 +6570,10 @@
         <v>83</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>83</v>
@@ -6580,10 +6584,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6609,13 +6613,13 @@
         <v>108</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -6665,7 +6669,7 @@
         <v>83</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
@@ -6686,10 +6690,10 @@
         <v>83</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>83</v>
@@ -6700,10 +6704,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6729,21 +6733,21 @@
         <v>174</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="S34" t="s" s="2">
         <v>83</v>
@@ -6785,7 +6789,7 @@
         <v>83</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
@@ -6806,10 +6810,10 @@
         <v>83</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>83</v>
@@ -6820,10 +6824,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6849,14 +6853,14 @@
         <v>108</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>83</v>
@@ -6905,7 +6909,7 @@
         <v>83</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
@@ -6926,10 +6930,10 @@
         <v>83</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>83</v>
@@ -6940,10 +6944,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6966,19 +6970,19 @@
         <v>95</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>83</v>
@@ -7027,7 +7031,7 @@
         <v>83</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
@@ -7048,10 +7052,10 @@
         <v>83</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>83</v>
@@ -7062,10 +7066,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -7091,16 +7095,16 @@
         <v>108</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>83</v>
@@ -7149,7 +7153,7 @@
         <v>83</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
@@ -7170,10 +7174,10 @@
         <v>83</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>83</v>
@@ -7184,14 +7188,14 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -7210,19 +7214,19 @@
         <v>95</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>83</v>
@@ -7250,10 +7254,10 @@
         <v>156</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>83</v>
@@ -7271,7 +7275,7 @@
         <v>83</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>94</v>
@@ -7286,30 +7290,30 @@
         <v>106</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7424,10 +7428,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7544,10 +7548,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7573,16 +7577,16 @@
         <v>152</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>83</v>
@@ -7619,7 +7623,7 @@
         <v>83</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AC41" s="2"/>
       <c r="AD41" t="s" s="2">
@@ -7629,7 +7633,7 @@
         <v>121</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -7650,10 +7654,10 @@
         <v>83</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>83</v>
@@ -7664,13 +7668,13 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C42" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D42" t="s" s="2">
         <v>83</v>
@@ -7695,16 +7699,16 @@
         <v>152</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>83</v>
@@ -7753,7 +7757,7 @@
         <v>83</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -7774,10 +7778,10 @@
         <v>83</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>83</v>
@@ -7788,10 +7792,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7906,10 +7910,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -8026,10 +8030,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -8055,23 +8059,23 @@
         <v>136</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q45" s="2"/>
       <c r="R45" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="S45" t="s" s="2">
         <v>83</v>
@@ -8113,7 +8117,7 @@
         <v>83</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -8134,10 +8138,10 @@
         <v>83</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>83</v>
@@ -8148,10 +8152,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8177,13 +8181,13 @@
         <v>108</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -8233,7 +8237,7 @@
         <v>83</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -8254,10 +8258,10 @@
         <v>83</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>83</v>
@@ -8268,10 +8272,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8297,21 +8301,21 @@
         <v>174</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q47" s="2"/>
       <c r="R47" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="S47" t="s" s="2">
         <v>83</v>
@@ -8353,7 +8357,7 @@
         <v>83</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -8374,10 +8378,10 @@
         <v>83</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>83</v>
@@ -8388,10 +8392,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8417,14 +8421,14 @@
         <v>108</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>83</v>
@@ -8473,7 +8477,7 @@
         <v>83</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -8494,10 +8498,10 @@
         <v>83</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>83</v>
@@ -8508,10 +8512,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8534,19 +8538,19 @@
         <v>95</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>83</v>
@@ -8595,7 +8599,7 @@
         <v>83</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -8616,10 +8620,10 @@
         <v>83</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>83</v>
@@ -8630,10 +8634,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8659,16 +8663,16 @@
         <v>108</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>83</v>
@@ -8717,7 +8721,7 @@
         <v>83</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -8738,10 +8742,10 @@
         <v>83</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>83</v>
@@ -8752,10 +8756,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8778,19 +8782,19 @@
         <v>95</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>83</v>
@@ -8839,7 +8843,7 @@
         <v>83</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8854,19 +8858,19 @@
         <v>106</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>83</v>
@@ -8874,10 +8878,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8900,16 +8904,16 @@
         <v>95</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -8959,7 +8963,7 @@
         <v>83</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8980,13 +8984,13 @@
         <v>83</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>83</v>
@@ -8994,14 +8998,14 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -9020,19 +9024,19 @@
         <v>95</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>83</v>
@@ -9081,7 +9085,7 @@
         <v>83</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -9096,19 +9100,19 @@
         <v>106</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>83</v>
@@ -9116,14 +9120,14 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -9142,19 +9146,19 @@
         <v>95</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>83</v>
@@ -9203,7 +9207,7 @@
         <v>83</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -9212,25 +9216,25 @@
         <v>94</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>83</v>
@@ -9238,10 +9242,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9267,13 +9271,13 @@
         <v>130</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -9323,7 +9327,7 @@
         <v>83</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -9344,13 +9348,13 @@
         <v>83</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>83</v>
@@ -9358,10 +9362,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9384,17 +9388,17 @@
         <v>95</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>83</v>
@@ -9443,7 +9447,7 @@
         <v>83</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -9458,19 +9462,19 @@
         <v>106</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>83</v>
@@ -9478,10 +9482,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9504,19 +9508,19 @@
         <v>95</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>83</v>
@@ -9553,17 +9557,17 @@
         <v>83</v>
       </c>
       <c r="AB57" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AC57" s="2"/>
       <c r="AD57" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE57" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -9572,7 +9576,7 @@
         <v>94</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>106</v>
@@ -9581,30 +9585,30 @@
         <v>83</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C58" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D58" t="s" s="2">
         <v>83</v>
@@ -9626,19 +9630,19 @@
         <v>95</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>83</v>
@@ -9687,7 +9691,7 @@
         <v>83</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -9696,7 +9700,7 @@
         <v>94</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>106</v>
@@ -9705,27 +9709,27 @@
         <v>83</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9748,19 +9752,19 @@
         <v>83</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>83</v>
@@ -9788,10 +9792,10 @@
         <v>156</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>83</v>
@@ -9809,7 +9813,7 @@
         <v>83</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9818,7 +9822,7 @@
         <v>94</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>106</v>
@@ -9833,7 +9837,7 @@
         <v>197</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>83</v>
@@ -9844,14 +9848,14 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -9870,19 +9874,19 @@
         <v>83</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>83</v>
@@ -9910,10 +9914,10 @@
         <v>156</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>83</v>
@@ -9931,7 +9935,7 @@
         <v>83</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -9949,27 +9953,27 @@
         <v>83</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9992,19 +9996,19 @@
         <v>83</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>83</v>
@@ -10053,7 +10057,7 @@
         <v>83</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -10074,10 +10078,10 @@
         <v>83</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>83</v>
@@ -10088,10 +10092,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10114,16 +10118,16 @@
         <v>83</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -10153,7 +10157,7 @@
       </c>
       <c r="Y62" s="2"/>
       <c r="Z62" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>83</v>
@@ -10171,7 +10175,7 @@
         <v>83</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -10189,27 +10193,27 @@
         <v>83</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10232,19 +10236,19 @@
         <v>83</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>83</v>
@@ -10273,7 +10277,7 @@
       </c>
       <c r="Y63" s="2"/>
       <c r="Z63" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>83</v>
@@ -10291,7 +10295,7 @@
         <v>83</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -10312,10 +10316,10 @@
         <v>83</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>83</v>
@@ -10326,10 +10330,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10352,16 +10356,16 @@
         <v>83</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -10411,7 +10415,7 @@
         <v>83</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -10429,27 +10433,27 @@
         <v>83</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10472,16 +10476,16 @@
         <v>83</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -10531,7 +10535,7 @@
         <v>83</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -10549,27 +10553,27 @@
         <v>83</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP65" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10592,19 +10596,19 @@
         <v>83</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>83</v>
@@ -10653,7 +10657,7 @@
         <v>83</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -10665,7 +10669,7 @@
         <v>83</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>83</v>
@@ -10674,10 +10678,10 @@
         <v>83</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>83</v>
@@ -10688,10 +10692,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10806,10 +10810,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10926,14 +10930,14 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
@@ -10955,16 +10959,16 @@
         <v>115</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="N69" t="s" s="2">
         <v>118</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>83</v>
@@ -11013,7 +11017,7 @@
         <v>83</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
@@ -11048,10 +11052,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11074,13 +11078,13 @@
         <v>83</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -11131,7 +11135,7 @@
         <v>83</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -11140,7 +11144,7 @@
         <v>94</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>106</v>
@@ -11152,10 +11156,10 @@
         <v>83</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>83</v>
@@ -11166,10 +11170,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11192,13 +11196,13 @@
         <v>83</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -11249,7 +11253,7 @@
         <v>83</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>81</v>
@@ -11258,7 +11262,7 @@
         <v>94</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AJ71" t="s" s="2">
         <v>106</v>
@@ -11270,10 +11274,10 @@
         <v>83</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>83</v>
@@ -11284,10 +11288,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11310,19 +11314,19 @@
         <v>83</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>83</v>
@@ -11350,10 +11354,10 @@
         <v>178</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>83</v>
@@ -11371,7 +11375,7 @@
         <v>83</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>
@@ -11389,13 +11393,13 @@
         <v>83</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>83</v>
@@ -11406,10 +11410,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11432,19 +11436,19 @@
         <v>83</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>83</v>
@@ -11472,10 +11476,10 @@
         <v>164</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>83</v>
@@ -11493,7 +11497,7 @@
         <v>83</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
@@ -11511,13 +11515,13 @@
         <v>83</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>83</v>
@@ -11528,10 +11532,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11554,17 +11558,17 @@
         <v>83</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>83</v>
@@ -11613,7 +11617,7 @@
         <v>83</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -11637,7 +11641,7 @@
         <v>83</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>83</v>
@@ -11648,10 +11652,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11677,10 +11681,10 @@
         <v>108</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -11731,7 +11735,7 @@
         <v>83</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>81</v>
@@ -11752,10 +11756,10 @@
         <v>83</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>83</v>
@@ -11766,10 +11770,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11792,16 +11796,16 @@
         <v>95</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -11851,7 +11855,7 @@
         <v>83</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>81</v>
@@ -11872,10 +11876,10 @@
         <v>83</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>83</v>
@@ -11886,10 +11890,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11912,16 +11916,16 @@
         <v>95</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -11971,7 +11975,7 @@
         <v>83</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>81</v>
@@ -11992,10 +11996,10 @@
         <v>83</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>83</v>
@@ -12006,10 +12010,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12017,7 +12021,7 @@
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="G78" t="s" s="2">
         <v>82</v>
@@ -12032,19 +12036,19 @@
         <v>95</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>83</v>
@@ -12081,7 +12085,7 @@
         <v>83</v>
       </c>
       <c r="AB78" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="AC78" s="2"/>
       <c r="AD78" t="s" s="2">
@@ -12091,7 +12095,7 @@
         <v>121</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>81</v>
@@ -12103,7 +12107,7 @@
         <v>83</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>83</v>
@@ -12112,10 +12116,10 @@
         <v>83</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>83</v>
@@ -12126,10 +12130,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12244,10 +12248,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12364,14 +12368,14 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
@@ -12393,16 +12397,16 @@
         <v>115</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="N81" t="s" s="2">
         <v>118</v>
       </c>
       <c r="O81" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>83</v>
@@ -12451,7 +12455,7 @@
         <v>83</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>81</v>
@@ -12486,10 +12490,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12512,19 +12516,19 @@
         <v>95</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>83</v>
@@ -12552,10 +12556,10 @@
         <v>156</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>83</v>
@@ -12573,7 +12577,7 @@
         <v>83</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>94</v>
@@ -12591,16 +12595,16 @@
         <v>83</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AO82" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AP82" t="s" s="2">
         <v>83</v>
@@ -12608,10 +12612,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12634,19 +12638,19 @@
         <v>95</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>83</v>
@@ -12674,10 +12678,10 @@
         <v>156</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="Z83" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>83</v>
@@ -12695,7 +12699,7 @@
         <v>83</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>81</v>
@@ -12704,7 +12708,7 @@
         <v>94</v>
       </c>
       <c r="AI83" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="AJ83" t="s" s="2">
         <v>106</v>
@@ -12713,27 +12717,27 @@
         <v>83</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP83" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12756,19 +12760,19 @@
         <v>83</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>83</v>
@@ -12796,10 +12800,10 @@
         <v>156</v>
       </c>
       <c r="Y84" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="Z84" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>83</v>
@@ -12817,7 +12821,7 @@
         <v>83</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>81</v>
@@ -12826,7 +12830,7 @@
         <v>94</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="AJ84" t="s" s="2">
         <v>106</v>
@@ -12841,7 +12845,7 @@
         <v>197</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>83</v>
@@ -12852,14 +12856,14 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
@@ -12878,19 +12882,19 @@
         <v>83</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="O85" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>83</v>
@@ -12918,10 +12922,10 @@
         <v>156</v>
       </c>
       <c r="Y85" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="Z85" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AA85" t="s" s="2">
         <v>83</v>
@@ -12939,7 +12943,7 @@
         <v>83</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>81</v>
@@ -12957,27 +12961,27 @@
         <v>83</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP85" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -13003,16 +13007,16 @@
         <v>84</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="O86" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>83</v>
@@ -13061,7 +13065,7 @@
         <v>83</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>81</v>
@@ -13082,10 +13086,10 @@
         <v>83</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>83</v>
@@ -13096,13 +13100,13 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C87" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="D87" t="s" s="2">
         <v>83</v>
@@ -13124,19 +13128,19 @@
         <v>95</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>83</v>
@@ -13185,7 +13189,7 @@
         <v>83</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>81</v>
@@ -13197,7 +13201,7 @@
         <v>83</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="AK87" t="s" s="2">
         <v>83</v>
@@ -13206,10 +13210,10 @@
         <v>83</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>83</v>
@@ -13220,10 +13224,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13338,10 +13342,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13458,14 +13462,14 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
@@ -13487,16 +13491,16 @@
         <v>115</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="N90" t="s" s="2">
         <v>118</v>
       </c>
       <c r="O90" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>83</v>
@@ -13545,7 +13549,7 @@
         <v>83</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>81</v>
@@ -13580,14 +13584,14 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
@@ -13606,19 +13610,19 @@
         <v>95</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>83</v>
@@ -13646,10 +13650,10 @@
         <v>156</v>
       </c>
       <c r="Y91" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Z91" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>83</v>
@@ -13667,7 +13671,7 @@
         <v>83</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>94</v>
@@ -13685,16 +13689,16 @@
         <v>83</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AO91" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AP91" t="s" s="2">
         <v>83</v>
@@ -13702,10 +13706,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13820,10 +13824,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13940,10 +13944,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13969,16 +13973,16 @@
         <v>152</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>83</v>
@@ -14015,7 +14019,7 @@
         <v>83</v>
       </c>
       <c r="AB94" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AC94" s="2"/>
       <c r="AD94" t="s" s="2">
@@ -14025,7 +14029,7 @@
         <v>121</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>81</v>
@@ -14046,10 +14050,10 @@
         <v>83</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>83</v>
@@ -14060,13 +14064,13 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="C95" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="D95" t="s" s="2">
         <v>83</v>
@@ -14091,16 +14095,16 @@
         <v>152</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O95" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>83</v>
@@ -14149,7 +14153,7 @@
         <v>83</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>81</v>
@@ -14170,10 +14174,10 @@
         <v>83</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>83</v>
@@ -14184,10 +14188,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14302,10 +14306,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14422,10 +14426,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14451,23 +14455,23 @@
         <v>136</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="O98" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q98" s="2"/>
       <c r="R98" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="S98" t="s" s="2">
         <v>83</v>
@@ -14509,7 +14513,7 @@
         <v>83</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>81</v>
@@ -14530,10 +14534,10 @@
         <v>83</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>83</v>
@@ -14544,10 +14548,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14573,13 +14577,13 @@
         <v>108</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
@@ -14629,7 +14633,7 @@
         <v>83</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>81</v>
@@ -14650,10 +14654,10 @@
         <v>83</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AO99" t="s" s="2">
         <v>83</v>
@@ -14664,10 +14668,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14693,21 +14697,21 @@
         <v>174</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q100" s="2"/>
       <c r="R100" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="S100" t="s" s="2">
         <v>83</v>
@@ -14749,7 +14753,7 @@
         <v>83</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>81</v>
@@ -14770,10 +14774,10 @@
         <v>83</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>83</v>
@@ -14784,10 +14788,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14813,14 +14817,14 @@
         <v>108</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>83</v>
@@ -14869,7 +14873,7 @@
         <v>83</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>81</v>
@@ -14890,10 +14894,10 @@
         <v>83</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AO101" t="s" s="2">
         <v>83</v>
@@ -14904,10 +14908,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14930,19 +14934,19 @@
         <v>95</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="O102" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>83</v>
@@ -14991,7 +14995,7 @@
         <v>83</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>81</v>
@@ -15012,10 +15016,10 @@
         <v>83</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>83</v>
@@ -15026,10 +15030,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -15055,16 +15059,16 @@
         <v>108</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="O103" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>83</v>
@@ -15113,7 +15117,7 @@
         <v>83</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>81</v>
@@ -15134,10 +15138,10 @@
         <v>83</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>83</v>
@@ -15148,10 +15152,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -15174,19 +15178,19 @@
         <v>95</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="O104" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>83</v>
@@ -15214,16 +15218,16 @@
         <v>156</v>
       </c>
       <c r="Y104" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="Z104" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AA104" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AB104" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AC104" s="2"/>
       <c r="AD104" t="s" s="2">
@@ -15233,7 +15237,7 @@
         <v>121</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>81</v>
@@ -15242,7 +15246,7 @@
         <v>94</v>
       </c>
       <c r="AI104" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="AJ104" t="s" s="2">
         <v>106</v>
@@ -15251,27 +15255,27 @@
         <v>83</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP104" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15386,10 +15390,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15506,10 +15510,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15532,19 +15536,19 @@
         <v>95</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="O107" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>83</v>
@@ -15593,7 +15597,7 @@
         <v>83</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>81</v>
@@ -15614,10 +15618,10 @@
         <v>83</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="AO107" t="s" s="2">
         <v>83</v>
@@ -15628,10 +15632,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15657,20 +15661,20 @@
         <v>174</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q108" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="R108" t="s" s="2">
         <v>83</v>
@@ -15691,13 +15695,13 @@
         <v>83</v>
       </c>
       <c r="X108" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Y108" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="Z108" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="AA108" t="s" s="2">
         <v>83</v>
@@ -15715,7 +15719,7 @@
         <v>83</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>81</v>
@@ -15736,10 +15740,10 @@
         <v>83</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="AO108" t="s" s="2">
         <v>83</v>
@@ -15750,10 +15754,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15779,14 +15783,14 @@
         <v>108</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="N109" s="2"/>
       <c r="O109" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>83</v>
@@ -15835,7 +15839,7 @@
         <v>83</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>81</v>
@@ -15856,10 +15860,10 @@
         <v>83</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="AN109" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="AO109" t="s" s="2">
         <v>83</v>
@@ -15870,10 +15874,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15899,21 +15903,21 @@
         <v>136</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="N110" s="2"/>
       <c r="O110" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q110" s="2"/>
       <c r="R110" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="S110" t="s" s="2">
         <v>83</v>
@@ -15955,7 +15959,7 @@
         <v>83</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>81</v>
@@ -15964,7 +15968,7 @@
         <v>94</v>
       </c>
       <c r="AI110" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="AJ110" t="s" s="2">
         <v>106</v>
@@ -15976,10 +15980,10 @@
         <v>83</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="AN110" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="AO110" t="s" s="2">
         <v>83</v>
@@ -15990,10 +15994,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -16019,23 +16023,23 @@
         <v>174</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="O111" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q111" s="2"/>
       <c r="R111" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="S111" t="s" s="2">
         <v>83</v>
@@ -16077,7 +16081,7 @@
         <v>83</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>81</v>
@@ -16098,10 +16102,10 @@
         <v>83</v>
       </c>
       <c r="AM111" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="AO111" t="s" s="2">
         <v>83</v>
@@ -16112,10 +16116,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -16138,19 +16142,19 @@
         <v>83</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="O112" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="P112" t="s" s="2">
         <v>83</v>
@@ -16178,10 +16182,10 @@
         <v>156</v>
       </c>
       <c r="Y112" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="Z112" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AA112" t="s" s="2">
         <v>83</v>
@@ -16199,7 +16203,7 @@
         <v>83</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>81</v>
@@ -16208,7 +16212,7 @@
         <v>94</v>
       </c>
       <c r="AI112" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="AJ112" t="s" s="2">
         <v>106</v>
@@ -16223,7 +16227,7 @@
         <v>197</v>
       </c>
       <c r="AN112" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AO112" t="s" s="2">
         <v>83</v>
@@ -16234,14 +16238,14 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="E113" s="2"/>
       <c r="F113" t="s" s="2">
@@ -16260,19 +16264,19 @@
         <v>83</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="O113" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>83</v>
@@ -16300,10 +16304,10 @@
         <v>156</v>
       </c>
       <c r="Y113" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="Z113" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AA113" t="s" s="2">
         <v>83</v>
@@ -16321,7 +16325,7 @@
         <v>83</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>81</v>
@@ -16339,27 +16343,27 @@
         <v>83</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AM113" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AN113" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AO113" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP113" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -16385,16 +16389,16 @@
         <v>84</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="O114" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>83</v>
@@ -16443,7 +16447,7 @@
         <v>83</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>81</v>
@@ -16464,10 +16468,10 @@
         <v>83</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AN114" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="AO114" t="s" s="2">
         <v>83</v>
@@ -16478,13 +16482,13 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C115" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="D115" t="s" s="2">
         <v>83</v>
@@ -16506,19 +16510,19 @@
         <v>95</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="O115" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>83</v>
@@ -16567,7 +16571,7 @@
         <v>83</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>81</v>
@@ -16579,7 +16583,7 @@
         <v>83</v>
       </c>
       <c r="AJ115" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="AK115" t="s" s="2">
         <v>83</v>
@@ -16588,10 +16592,10 @@
         <v>83</v>
       </c>
       <c r="AM115" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="AN115" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="AO115" t="s" s="2">
         <v>83</v>
@@ -16602,10 +16606,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16720,10 +16724,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16840,14 +16844,14 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="E118" s="2"/>
       <c r="F118" t="s" s="2">
@@ -16869,16 +16873,16 @@
         <v>115</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="N118" t="s" s="2">
         <v>118</v>
       </c>
       <c r="O118" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P118" t="s" s="2">
         <v>83</v>
@@ -16927,7 +16931,7 @@
         <v>83</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>81</v>
@@ -16962,10 +16966,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16988,19 +16992,19 @@
         <v>95</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="O119" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="P119" t="s" s="2">
         <v>83</v>
@@ -17028,10 +17032,10 @@
         <v>156</v>
       </c>
       <c r="Y119" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Z119" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AA119" t="s" s="2">
         <v>83</v>
@@ -17049,7 +17053,7 @@
         <v>83</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>94</v>
@@ -17067,16 +17071,16 @@
         <v>83</v>
       </c>
       <c r="AL119" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="AM119" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AN119" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AO119" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AP119" t="s" s="2">
         <v>83</v>
@@ -17084,10 +17088,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -17202,10 +17206,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -17322,10 +17326,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -17351,16 +17355,16 @@
         <v>152</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="N122" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O122" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="P122" t="s" s="2">
         <v>83</v>
@@ -17397,7 +17401,7 @@
         <v>83</v>
       </c>
       <c r="AB122" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AC122" s="2"/>
       <c r="AD122" t="s" s="2">
@@ -17407,7 +17411,7 @@
         <v>121</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>81</v>
@@ -17428,10 +17432,10 @@
         <v>83</v>
       </c>
       <c r="AM122" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AN122" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AO122" t="s" s="2">
         <v>83</v>
@@ -17442,13 +17446,13 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="C123" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="D123" t="s" s="2">
         <v>83</v>
@@ -17473,16 +17477,16 @@
         <v>152</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="N123" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O123" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>83</v>
@@ -17531,7 +17535,7 @@
         <v>83</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>81</v>
@@ -17552,10 +17556,10 @@
         <v>83</v>
       </c>
       <c r="AM123" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AN123" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AO123" t="s" s="2">
         <v>83</v>
@@ -17566,10 +17570,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17684,10 +17688,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17804,10 +17808,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17833,23 +17837,23 @@
         <v>136</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="N126" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="O126" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="P126" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q126" s="2"/>
       <c r="R126" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="S126" t="s" s="2">
         <v>83</v>
@@ -17891,7 +17895,7 @@
         <v>83</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>81</v>
@@ -17912,10 +17916,10 @@
         <v>83</v>
       </c>
       <c r="AM126" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AN126" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AO126" t="s" s="2">
         <v>83</v>
@@ -17926,10 +17930,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17955,13 +17959,13 @@
         <v>108</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="N127" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="O127" s="2"/>
       <c r="P127" t="s" s="2">
@@ -18011,7 +18015,7 @@
         <v>83</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>81</v>
@@ -18032,10 +18036,10 @@
         <v>83</v>
       </c>
       <c r="AM127" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AN127" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AO127" t="s" s="2">
         <v>83</v>
@@ -18046,10 +18050,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -18075,21 +18079,21 @@
         <v>174</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="N128" s="2"/>
       <c r="O128" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="P128" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q128" s="2"/>
       <c r="R128" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="S128" t="s" s="2">
         <v>83</v>
@@ -18131,7 +18135,7 @@
         <v>83</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>81</v>
@@ -18152,10 +18156,10 @@
         <v>83</v>
       </c>
       <c r="AM128" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AN128" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AO128" t="s" s="2">
         <v>83</v>
@@ -18166,10 +18170,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -18195,14 +18199,14 @@
         <v>108</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="N129" s="2"/>
       <c r="O129" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="P129" t="s" s="2">
         <v>83</v>
@@ -18251,7 +18255,7 @@
         <v>83</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>81</v>
@@ -18272,10 +18276,10 @@
         <v>83</v>
       </c>
       <c r="AM129" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AN129" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AO129" t="s" s="2">
         <v>83</v>
@@ -18286,10 +18290,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -18312,19 +18316,19 @@
         <v>95</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="N130" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="O130" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="P130" t="s" s="2">
         <v>83</v>
@@ -18373,7 +18377,7 @@
         <v>83</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>81</v>
@@ -18394,10 +18398,10 @@
         <v>83</v>
       </c>
       <c r="AM130" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AN130" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AO130" t="s" s="2">
         <v>83</v>
@@ -18408,10 +18412,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -18437,16 +18441,16 @@
         <v>108</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="N131" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="O131" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="P131" t="s" s="2">
         <v>83</v>
@@ -18495,7 +18499,7 @@
         <v>83</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>81</v>
@@ -18516,10 +18520,10 @@
         <v>83</v>
       </c>
       <c r="AM131" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AN131" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AO131" t="s" s="2">
         <v>83</v>
@@ -18530,10 +18534,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -18556,19 +18560,19 @@
         <v>95</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="O132" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="P132" t="s" s="2">
         <v>83</v>
@@ -18596,16 +18600,16 @@
         <v>156</v>
       </c>
       <c r="Y132" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="Z132" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AA132" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AB132" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AC132" s="2"/>
       <c r="AD132" t="s" s="2">
@@ -18615,7 +18619,7 @@
         <v>121</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>81</v>
@@ -18624,7 +18628,7 @@
         <v>94</v>
       </c>
       <c r="AI132" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="AJ132" t="s" s="2">
         <v>106</v>
@@ -18633,27 +18637,27 @@
         <v>83</v>
       </c>
       <c r="AL132" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="AM132" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AN132" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AO132" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP132" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -18768,10 +18772,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -18888,10 +18892,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -18914,19 +18918,19 @@
         <v>95</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="N135" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="O135" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="P135" t="s" s="2">
         <v>83</v>
@@ -18975,7 +18979,7 @@
         <v>83</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>81</v>
@@ -18996,10 +19000,10 @@
         <v>83</v>
       </c>
       <c r="AM135" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="AN135" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="AO135" t="s" s="2">
         <v>83</v>
@@ -19010,10 +19014,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -19039,20 +19043,20 @@
         <v>174</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="N136" s="2"/>
       <c r="O136" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="P136" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q136" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="R136" t="s" s="2">
         <v>83</v>
@@ -19073,13 +19077,13 @@
         <v>83</v>
       </c>
       <c r="X136" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Y136" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="Z136" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="AA136" t="s" s="2">
         <v>83</v>
@@ -19097,7 +19101,7 @@
         <v>83</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>81</v>
@@ -19118,10 +19122,10 @@
         <v>83</v>
       </c>
       <c r="AM136" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="AN136" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="AO136" t="s" s="2">
         <v>83</v>
@@ -19132,10 +19136,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -19161,14 +19165,14 @@
         <v>108</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="N137" s="2"/>
       <c r="O137" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="P137" t="s" s="2">
         <v>83</v>
@@ -19217,7 +19221,7 @@
         <v>83</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>81</v>
@@ -19238,10 +19242,10 @@
         <v>83</v>
       </c>
       <c r="AM137" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="AN137" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="AO137" t="s" s="2">
         <v>83</v>
@@ -19252,10 +19256,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -19281,21 +19285,21 @@
         <v>136</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="N138" s="2"/>
       <c r="O138" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="P138" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q138" s="2"/>
       <c r="R138" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="S138" t="s" s="2">
         <v>83</v>
@@ -19337,7 +19341,7 @@
         <v>83</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>81</v>
@@ -19346,7 +19350,7 @@
         <v>94</v>
       </c>
       <c r="AI138" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="AJ138" t="s" s="2">
         <v>106</v>
@@ -19358,10 +19362,10 @@
         <v>83</v>
       </c>
       <c r="AM138" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="AN138" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="AO138" t="s" s="2">
         <v>83</v>
@@ -19372,10 +19376,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -19401,23 +19405,23 @@
         <v>174</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="N139" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="O139" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="P139" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q139" s="2"/>
       <c r="R139" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="S139" t="s" s="2">
         <v>83</v>
@@ -19459,7 +19463,7 @@
         <v>83</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>81</v>
@@ -19480,10 +19484,10 @@
         <v>83</v>
       </c>
       <c r="AM139" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="AN139" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="AO139" t="s" s="2">
         <v>83</v>
@@ -19494,10 +19498,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -19520,19 +19524,19 @@
         <v>83</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="N140" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="O140" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="P140" t="s" s="2">
         <v>83</v>
@@ -19560,10 +19564,10 @@
         <v>156</v>
       </c>
       <c r="Y140" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="Z140" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AA140" t="s" s="2">
         <v>83</v>
@@ -19581,7 +19585,7 @@
         <v>83</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>81</v>
@@ -19590,7 +19594,7 @@
         <v>94</v>
       </c>
       <c r="AI140" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="AJ140" t="s" s="2">
         <v>106</v>
@@ -19605,7 +19609,7 @@
         <v>197</v>
       </c>
       <c r="AN140" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AO140" t="s" s="2">
         <v>83</v>
@@ -19616,14 +19620,14 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="E141" s="2"/>
       <c r="F141" t="s" s="2">
@@ -19642,19 +19646,19 @@
         <v>83</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="N141" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="O141" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="P141" t="s" s="2">
         <v>83</v>
@@ -19682,10 +19686,10 @@
         <v>156</v>
       </c>
       <c r="Y141" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="Z141" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AA141" t="s" s="2">
         <v>83</v>
@@ -19703,7 +19707,7 @@
         <v>83</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>81</v>
@@ -19721,27 +19725,27 @@
         <v>83</v>
       </c>
       <c r="AL141" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AM141" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AN141" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AO141" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP141" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -19767,16 +19771,16 @@
         <v>84</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="N142" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="O142" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="P142" t="s" s="2">
         <v>83</v>
@@ -19825,7 +19829,7 @@
         <v>83</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>81</v>
@@ -19846,10 +19850,10 @@
         <v>83</v>
       </c>
       <c r="AM142" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AN142" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="AO142" t="s" s="2">
         <v>83</v>
@@ -19860,13 +19864,13 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C143" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="D143" t="s" s="2">
         <v>83</v>
@@ -19888,19 +19892,19 @@
         <v>95</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="N143" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="O143" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="P143" t="s" s="2">
         <v>83</v>
@@ -19949,7 +19953,7 @@
         <v>83</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>81</v>
@@ -19961,7 +19965,7 @@
         <v>83</v>
       </c>
       <c r="AJ143" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="AK143" t="s" s="2">
         <v>83</v>
@@ -19970,10 +19974,10 @@
         <v>83</v>
       </c>
       <c r="AM143" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="AN143" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="AO143" t="s" s="2">
         <v>83</v>
@@ -19984,10 +19988,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -20102,10 +20106,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -20222,14 +20226,14 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="E146" s="2"/>
       <c r="F146" t="s" s="2">
@@ -20251,16 +20255,16 @@
         <v>115</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="N146" t="s" s="2">
         <v>118</v>
       </c>
       <c r="O146" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P146" t="s" s="2">
         <v>83</v>
@@ -20309,7 +20313,7 @@
         <v>83</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>81</v>
@@ -20344,10 +20348,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -20370,19 +20374,19 @@
         <v>95</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="N147" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="O147" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="P147" t="s" s="2">
         <v>83</v>
@@ -20410,10 +20414,10 @@
         <v>156</v>
       </c>
       <c r="Y147" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Z147" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AA147" t="s" s="2">
         <v>83</v>
@@ -20431,7 +20435,7 @@
         <v>83</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>94</v>
@@ -20449,16 +20453,16 @@
         <v>83</v>
       </c>
       <c r="AL147" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="AM147" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AN147" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AO147" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AP147" t="s" s="2">
         <v>83</v>
@@ -20466,10 +20470,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -20584,10 +20588,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -20704,10 +20708,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -20733,16 +20737,16 @@
         <v>152</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="N150" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O150" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="P150" t="s" s="2">
         <v>83</v>
@@ -20779,10 +20783,10 @@
         <v>83</v>
       </c>
       <c r="AB150" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AC150" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="AD150" t="s" s="2">
         <v>83</v>
@@ -20791,7 +20795,7 @@
         <v>121</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>81</v>
@@ -20812,10 +20816,10 @@
         <v>83</v>
       </c>
       <c r="AM150" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AN150" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AO150" t="s" s="2">
         <v>83</v>
@@ -20826,13 +20830,13 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="C151" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="D151" t="s" s="2">
         <v>83</v>
@@ -20857,16 +20861,16 @@
         <v>152</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="N151" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O151" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="P151" t="s" s="2">
         <v>83</v>
@@ -20915,7 +20919,7 @@
         <v>83</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>81</v>
@@ -20936,10 +20940,10 @@
         <v>83</v>
       </c>
       <c r="AM151" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AN151" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AO151" t="s" s="2">
         <v>83</v>
@@ -20950,10 +20954,10 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -21068,10 +21072,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -21188,10 +21192,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -21217,16 +21221,16 @@
         <v>136</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="N154" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="O154" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="P154" t="s" s="2">
         <v>83</v>
@@ -21236,7 +21240,7 @@
         <v>83</v>
       </c>
       <c r="S154" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="T154" t="s" s="2">
         <v>83</v>
@@ -21275,7 +21279,7 @@
         <v>83</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>81</v>
@@ -21296,10 +21300,10 @@
         <v>83</v>
       </c>
       <c r="AM154" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AN154" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AO154" t="s" s="2">
         <v>83</v>
@@ -21310,10 +21314,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -21339,13 +21343,13 @@
         <v>108</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="N155" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="O155" s="2"/>
       <c r="P155" t="s" s="2">
@@ -21395,7 +21399,7 @@
         <v>83</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>81</v>
@@ -21416,10 +21420,10 @@
         <v>83</v>
       </c>
       <c r="AM155" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AN155" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AO155" t="s" s="2">
         <v>83</v>
@@ -21430,10 +21434,10 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -21459,14 +21463,14 @@
         <v>174</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="N156" s="2"/>
       <c r="O156" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="P156" t="s" s="2">
         <v>83</v>
@@ -21476,7 +21480,7 @@
         <v>83</v>
       </c>
       <c r="S156" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="T156" t="s" s="2">
         <v>83</v>
@@ -21515,7 +21519,7 @@
         <v>83</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>81</v>
@@ -21536,10 +21540,10 @@
         <v>83</v>
       </c>
       <c r="AM156" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AN156" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AO156" t="s" s="2">
         <v>83</v>
@@ -21550,10 +21554,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -21579,14 +21583,14 @@
         <v>108</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="N157" s="2"/>
       <c r="O157" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="P157" t="s" s="2">
         <v>83</v>
@@ -21635,7 +21639,7 @@
         <v>83</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>81</v>
@@ -21656,10 +21660,10 @@
         <v>83</v>
       </c>
       <c r="AM157" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AN157" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AO157" t="s" s="2">
         <v>83</v>
@@ -21670,10 +21674,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -21696,19 +21700,19 @@
         <v>95</v>
       </c>
       <c r="K158" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="N158" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="O158" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="P158" t="s" s="2">
         <v>83</v>
@@ -21757,7 +21761,7 @@
         <v>83</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>81</v>
@@ -21778,10 +21782,10 @@
         <v>83</v>
       </c>
       <c r="AM158" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AN158" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AO158" t="s" s="2">
         <v>83</v>
@@ -21792,10 +21796,10 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -21821,16 +21825,16 @@
         <v>108</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="N159" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="O159" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="P159" t="s" s="2">
         <v>83</v>
@@ -21879,7 +21883,7 @@
         <v>83</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>81</v>
@@ -21900,10 +21904,10 @@
         <v>83</v>
       </c>
       <c r="AM159" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AN159" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AO159" t="s" s="2">
         <v>83</v>
@@ -21914,10 +21918,10 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -21940,19 +21944,19 @@
         <v>95</v>
       </c>
       <c r="K160" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="N160" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="O160" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="P160" t="s" s="2">
         <v>83</v>
@@ -21980,10 +21984,10 @@
         <v>156</v>
       </c>
       <c r="Y160" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="Z160" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AA160" t="s" s="2">
         <v>83</v>
@@ -22001,7 +22005,7 @@
         <v>83</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>81</v>
@@ -22010,7 +22014,7 @@
         <v>94</v>
       </c>
       <c r="AI160" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="AJ160" t="s" s="2">
         <v>106</v>
@@ -22019,27 +22023,27 @@
         <v>83</v>
       </c>
       <c r="AL160" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="AM160" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AN160" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AO160" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP160" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -22062,19 +22066,19 @@
         <v>83</v>
       </c>
       <c r="K161" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="N161" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="O161" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="P161" t="s" s="2">
         <v>83</v>
@@ -22102,10 +22106,10 @@
         <v>156</v>
       </c>
       <c r="Y161" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="Z161" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AA161" t="s" s="2">
         <v>83</v>
@@ -22123,7 +22127,7 @@
         <v>83</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>81</v>
@@ -22132,7 +22136,7 @@
         <v>94</v>
       </c>
       <c r="AI161" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="AJ161" t="s" s="2">
         <v>106</v>
@@ -22147,7 +22151,7 @@
         <v>197</v>
       </c>
       <c r="AN161" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AO161" t="s" s="2">
         <v>83</v>
@@ -22158,14 +22162,14 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="E162" s="2"/>
       <c r="F162" t="s" s="2">
@@ -22184,19 +22188,19 @@
         <v>83</v>
       </c>
       <c r="K162" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="N162" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="O162" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="P162" t="s" s="2">
         <v>83</v>
@@ -22224,10 +22228,10 @@
         <v>156</v>
       </c>
       <c r="Y162" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="Z162" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AA162" t="s" s="2">
         <v>83</v>
@@ -22245,7 +22249,7 @@
         <v>83</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>81</v>
@@ -22263,27 +22267,27 @@
         <v>83</v>
       </c>
       <c r="AL162" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AM162" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AN162" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AO162" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP162" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -22309,16 +22313,16 @@
         <v>84</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="N163" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="O163" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="P163" t="s" s="2">
         <v>83</v>
@@ -22367,7 +22371,7 @@
         <v>83</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>81</v>
@@ -22388,10 +22392,10 @@
         <v>83</v>
       </c>
       <c r="AM163" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AN163" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="AO163" t="s" s="2">
         <v>83</v>

--- a/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-08T07:32:57+00:00</t>
+    <t>2025-10-08T12:04:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.1.0</t>
+    <t>2.2.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-08T12:04:30+00:00</t>
+    <t>2025-10-08T16:01:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-30T10:25:45+00:00</t>
+    <t>2026-02-04T13:09:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-04T13:09:39+00:00</t>
+    <t>2026-02-09T06:47:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-09T06:47:58+00:00</t>
+    <t>2026-02-11T16:15:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-11T16:15:37+00:00</t>
+    <t>2026-02-17T10:02:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-17T10:02:14+00:00</t>
+    <t>2026-02-23T09:26:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T09:26:22+00:00</t>
+    <t>2026-02-23T10:39:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T10:39:10+00:00</t>
+    <t>2026-02-23T12:56:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6288" uniqueCount="756">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6290" uniqueCount="756">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-20T07:09:47+00:00</t>
+    <t>2026-03-25T10:22:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -15149,7 +15149,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="104" hidden="true">
+    <row r="104">
       <c r="A104" t="s" s="2">
         <v>642</v>
       </c>
@@ -15226,14 +15226,16 @@
         <v>83</v>
       </c>
       <c r="AB104" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="AC104" s="2"/>
+        <v>83</v>
+      </c>
+      <c r="AC104" t="s" s="2">
+        <v>83</v>
+      </c>
       <c r="AD104" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE104" t="s" s="2">
-        <v>121</v>
+        <v>83</v>
       </c>
       <c r="AF104" t="s" s="2">
         <v>590</v>
@@ -18531,7 +18533,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="132" hidden="true">
+    <row r="132">
       <c r="A132" t="s" s="2">
         <v>719</v>
       </c>
@@ -18608,14 +18610,16 @@
         <v>83</v>
       </c>
       <c r="AB132" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="AC132" s="2"/>
+        <v>83</v>
+      </c>
+      <c r="AC132" t="s" s="2">
+        <v>83</v>
+      </c>
       <c r="AD132" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE132" t="s" s="2">
-        <v>121</v>
+        <v>83</v>
       </c>
       <c r="AF132" t="s" s="2">
         <v>590</v>

--- a/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T10:22:11+00:00</t>
+    <t>2026-03-25T10:22:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T10:22:40+00:00</t>
+    <t>2026-03-25T10:25:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T10:25:13+00:00</t>
+    <t>2026-03-25T15:00:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T15:00:47+00:00</t>
+    <t>2026-03-31T09:16:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>France</t>
+    <t>France (la)</t>
   </si>
   <si>
     <t>Description</t>

--- a/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-31T09:16:18+00:00</t>
+    <t>2026-05-07T06:38:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-27T13:50:40+00:00</t>
+    <t>2026-05-27T14:53:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-27T14:53:55+00:00</t>
+    <t>2026-05-28T14:22:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-28T14:22:24+00:00</t>
+    <t>2026-06-12T14:04:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T14:04:24+00:00</t>
+    <t>2026-06-12T14:05:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T14:05:00+00:00</t>
+    <t>2026-06-12T14:35:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T14:35:23+00:00</t>
+    <t>2026-06-26T12:32:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-26T12:32:04+00:00</t>
+    <t>2026-06-29T09:30:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T09:30:52+00:00</t>
+    <t>2026-07-22T12:21:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T12:21:07+00:00</t>
+    <t>2026-07-27T15:02:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T15:02:31+00:00</t>
+    <t>2026-08-03T12:52:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T12:52:25+00:00</t>
+    <t>2026-08-04T12:22:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-04T12:22:31+00:00</t>
+    <t>2026-08-04T12:29:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
+++ b/main/ig/StructureDefinition-fr-core-observation-bp.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-04T12:29:23+00:00</t>
+    <t>2026-08-10T16:34:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
